--- a/public/planilla.xlsx
+++ b/public/planilla.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -408,56 +408,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>PLANILLA DE REGISTRO DE ALUMNOS - NeuroDivisión</v>
+        <v>Nombre</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Apellido</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Sexo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Fecha de nacimiento</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Correo apoderado (opcional)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Instrucciones: Complete los datos desde la fila 5 en adelante.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Sexo: ingrese MASCULINO o FEMENINO. Fecha de nacimiento: formato DD/MM/AAAA.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Apellido</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Sexo</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Fecha de nacimiento</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Correo apoderado (opcional)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
         <v>Juan</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B2" t="str">
         <v>Pérez</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C2" t="str">
         <v>MASCULINO</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D2" t="str">
         <v>2015-03-21</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E2" t="str">
         <v>apoderado@email.com</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>